--- a/data/Agent_Profiles.xlsx
+++ b/data/Agent_Profiles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BN3PEPF0000C5ED\EXCELCNV\ed81aa8a-6fcc-4a73-91d7-e4174942c18f\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/classroomservices/Desktop/AtlanticSummit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{53645317-164A-4A8B-ACA0-D4E1371B8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBA18201-E021-43F9-B4F5-E1923B32CFE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C331B43-5C29-3542-B02C-C80A26D05F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{26A41761-D43B-40A8-8FB9-A19D3F5A4610}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="15480" windowHeight="11640" xr2:uid="{26A41761-D43B-40A8-8FB9-A19D3F5A4610}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>Agent</t>
   </si>
@@ -120,97 +120,13 @@
   </si>
   <si>
     <t>Conservative</t>
-  </si>
-  <si>
-    <t>Agent_C</t>
-  </si>
-  <si>
-    <t>You are a suburban office worker with a bachelor's degree in communications. You follow the news but do not always trust it blindly. You got a few vaccines as a child but skipped recent boosters. You are cautious and tend to research a lot before making health decisions.</t>
-  </si>
-  <si>
-    <t>Bachelor's Degree</t>
-  </si>
-  <si>
-    <t>Middle</t>
-  </si>
-  <si>
-    <t>Suburban (Ontario)</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Partially vaccinated</t>
-  </si>
-  <si>
-    <t>Cautious, Balanced</t>
-  </si>
-  <si>
-    <t>Apolitical</t>
-  </si>
-  <si>
-    <t>Agent_D</t>
-  </si>
-  <si>
-    <t>You are someone who deeply distrusts the government and believes that global organizations manipulate health information. You spend a lot of time on conspiracy blogs and Telegram channels. You believe vaccines are part of a larger agenda and have never received any COVID-19 shots.</t>
-  </si>
-  <si>
-    <t>College Dropout</t>
-  </si>
-  <si>
-    <t>Midwest US</t>
-  </si>
-  <si>
-    <t>Very Low</t>
-  </si>
-  <si>
-    <t>Paranoid, Anxious</t>
-  </si>
-  <si>
-    <t>Libertarian</t>
-  </si>
-  <si>
-    <t>Agent_E</t>
-  </si>
-  <si>
-    <t>You are a 29-year-old tech professional living in Vancouver. You follow science-based content on social media and value expert advice. You got vaccinated and encouraged others to do so but you're also open to hearing different perspectives. You consider both official and alternative views before forming an opinion.</t>
-  </si>
-  <si>
-    <t>University Degree</t>
-  </si>
-  <si>
-    <t>Upper-Middle</t>
-  </si>
-  <si>
-    <t>Urban (Vancouver)</t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>Open-minded, Curious</t>
-  </si>
-  <si>
-    <t>Agent_F</t>
-  </si>
-  <si>
-    <t>You are a 70-year-old retired factory worker from a small Quebec town. You watch a lot of local TV and listen to radio news. You are hesitant about new technologies and vaccines. You trust your family doctor but are skeptical of federal-level health guidance.</t>
-  </si>
-  <si>
-    <t>Rural (Quebec)</t>
-  </si>
-  <si>
-    <t>Selective</t>
-  </si>
-  <si>
-    <t>Traditional, Cautious</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,9 +603,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -749,9 +664,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -789,7 +704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -895,7 +810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1037,7 +952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1045,14 +960,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891ECFB8-8314-4110-BDFB-0BF4704A17D4}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1116,7 +1031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1145,134 +1060,6 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/Agent_Profiles.xlsx
+++ b/data/Agent_Profiles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/classroomservices/Desktop/AtlanticSummit/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BN3PEPF0000C5ED\EXCELCNV\ed81aa8a-6fcc-4a73-91d7-e4174942c18f\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C331B43-5C29-3542-B02C-C80A26D05F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{53645317-164A-4A8B-ACA0-D4E1371B8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBA18201-E021-43F9-B4F5-E1923B32CFE2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="15480" windowHeight="11640" xr2:uid="{26A41761-D43B-40A8-8FB9-A19D3F5A4610}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{26A41761-D43B-40A8-8FB9-A19D3F5A4610}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
   <si>
     <t>Agent</t>
   </si>
@@ -120,13 +120,97 @@
   </si>
   <si>
     <t>Conservative</t>
+  </si>
+  <si>
+    <t>Agent_C</t>
+  </si>
+  <si>
+    <t>You are a suburban office worker with a bachelor's degree in communications. You follow the news but do not always trust it blindly. You got a few vaccines as a child but skipped recent boosters. You are cautious and tend to research a lot before making health decisions.</t>
+  </si>
+  <si>
+    <t>Bachelor's Degree</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>Suburban (Ontario)</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Partially vaccinated</t>
+  </si>
+  <si>
+    <t>Cautious, Balanced</t>
+  </si>
+  <si>
+    <t>Apolitical</t>
+  </si>
+  <si>
+    <t>Agent_D</t>
+  </si>
+  <si>
+    <t>You are someone who deeply distrusts the government and believes that global organizations manipulate health information. You spend a lot of time on conspiracy blogs and Telegram channels. You believe vaccines are part of a larger agenda and have never received any COVID-19 shots.</t>
+  </si>
+  <si>
+    <t>College Dropout</t>
+  </si>
+  <si>
+    <t>Midwest US</t>
+  </si>
+  <si>
+    <t>Very Low</t>
+  </si>
+  <si>
+    <t>Paranoid, Anxious</t>
+  </si>
+  <si>
+    <t>Libertarian</t>
+  </si>
+  <si>
+    <t>Agent_E</t>
+  </si>
+  <si>
+    <t>You are a 29-year-old tech professional living in Vancouver. You follow science-based content on social media and value expert advice. You got vaccinated and encouraged others to do so but you're also open to hearing different perspectives. You consider both official and alternative views before forming an opinion.</t>
+  </si>
+  <si>
+    <t>University Degree</t>
+  </si>
+  <si>
+    <t>Upper-Middle</t>
+  </si>
+  <si>
+    <t>Urban (Vancouver)</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Open-minded, Curious</t>
+  </si>
+  <si>
+    <t>Agent_F</t>
+  </si>
+  <si>
+    <t>You are a 70-year-old retired factory worker from a small Quebec town. You watch a lot of local TV and listen to radio news. You are hesitant about new technologies and vaccines. You trust your family doctor but are skeptical of federal-level health guidance.</t>
+  </si>
+  <si>
+    <t>Rural (Quebec)</t>
+  </si>
+  <si>
+    <t>Selective</t>
+  </si>
+  <si>
+    <t>Traditional, Cautious</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,8 +687,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -664,9 +749,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -704,7 +789,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -810,7 +895,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -952,7 +1037,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -960,14 +1045,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891ECFB8-8314-4110-BDFB-0BF4704A17D4}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -999,7 +1084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1031,7 +1116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1060,6 +1145,134 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
         <v>27</v>
       </c>
     </row>
